--- a/erp-server/erp-server-file/src/main/resources/excel/wms/packingDetailMergeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/packingDetailMergeExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -103,7 +103,7 @@
     <t>{.packQty}</t>
   </si>
   <si>
-    <t>{.packageWeightStr}</t>
+    <t>{.packageWeight}</t>
   </si>
   <si>
     <t>{.length}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/packingDetailMergeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/packingDetailMergeExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>装箱任务</t>
   </si>
@@ -58,6 +58,9 @@
     <t>装箱SKU</t>
   </si>
   <si>
+    <t>客户PO号</t>
+  </si>
+  <si>
     <t>数量</t>
   </si>
   <si>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>{.sku}</t>
+  </si>
+  <si>
+    <t>{.customerPO}</t>
   </si>
   <si>
     <t>{.packQty}</t>
@@ -1111,28 +1117,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="21.125" customWidth="1"/>
     <col min="2" max="2" width="19.125" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="16.5" customWidth="1"/>
-    <col min="10" max="11" width="20.5" customWidth="1"/>
-    <col min="12" max="12" width="22.375" customWidth="1"/>
-    <col min="13" max="13" width="24.75" customWidth="1"/>
-    <col min="14" max="14" width="17.75" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="8.875" customWidth="1"/>
-    <col min="19" max="19" width="31.25" customWidth="1"/>
-    <col min="21" max="21" width="17.375" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="9" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="12" width="20.5" customWidth="1"/>
+    <col min="13" max="13" width="22.375" customWidth="1"/>
+    <col min="14" max="14" width="24.75" customWidth="1"/>
+    <col min="15" max="15" width="17.75" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="10.375" customWidth="1"/>
+    <col min="19" max="19" width="8.875" customWidth="1"/>
+    <col min="20" max="20" width="31.25" customWidth="1"/>
+    <col min="22" max="22" width="17.375" customWidth="1"/>
+    <col min="24" max="24" width="9.375" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1175,49 +1181,55 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" spans="1:15">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
